--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26957.34</v>
+        <v>26845.29</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>558501.78</v>
+        <v>556180.29</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>78226.38</v>
+        <v>77589.44</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>425249.38</v>
+        <v>421786.91</v>
       </c>
     </row>
     <row r="6">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7443.37</v>
+        <v>7459.5</v>
       </c>
     </row>
     <row r="7">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>253458.04</v>
+        <v>254565.52</v>
       </c>
     </row>
     <row r="8">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>22619.74</v>
+        <v>22718.57</v>
       </c>
     </row>
     <row r="9">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18428.71</v>
+        <v>18509.23</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25339.34</v>
+        <v>25450.06</v>
       </c>
     </row>
     <row r="11">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19954.43</v>
+        <v>20041.62</v>
       </c>
     </row>
     <row r="12">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>19759.86</v>
+        <v>19846.2</v>
       </c>
     </row>
     <row r="13">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10842.94</v>
+        <v>10787.97</v>
       </c>
     </row>
     <row r="14">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>46636.29</v>
+        <v>46399.86</v>
       </c>
     </row>
     <row r="15">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34219.61</v>
+        <v>34277.51</v>
       </c>
     </row>
     <row r="16">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>427192.07</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="17">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>62871.94</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="18">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8493.15</v>
+        <v>8545.73</v>
       </c>
     </row>
     <row r="19">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>74363.67999999999</v>
+        <v>74806.8</v>
       </c>
     </row>
     <row r="20">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>222685.76</v>
+        <v>224012.71</v>
       </c>
     </row>
     <row r="21">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8291.67</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="22">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>40568.04</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="23">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32184.57</v>
+        <v>32127.7</v>
       </c>
     </row>
     <row r="24">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>42396.62</v>
+        <v>42321.72</v>
       </c>
     </row>
     <row r="25">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7542.22</v>
+        <v>7535.11</v>
       </c>
     </row>
     <row r="26">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>48857.96</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="27">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>17554</v>
+        <v>17432.29</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>72341.53999999999</v>
+        <v>71839.97</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>112086.39</v>
+        <v>111309.26</v>
       </c>
     </row>
     <row r="30">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>72413.42999999999</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="31">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15657.11</v>
+        <v>15639.94</v>
       </c>
     </row>
     <row r="32">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>50956.5</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7941.53</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="34">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27839.4</v>
+        <v>27702.12</v>
       </c>
     </row>
     <row r="35">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>45818.31</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="36">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43664.84</v>
+        <v>43455.72</v>
       </c>
     </row>
     <row r="37">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>59818.67</v>
+        <v>59522.39</v>
       </c>
     </row>
     <row r="38">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>56814.7</v>
+        <v>56533.3</v>
       </c>
     </row>
     <row r="39">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>76218.81</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="40">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>77492.14</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="41">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19714.43</v>
+        <v>19615.96</v>
       </c>
     </row>
     <row r="42">
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>37857.1</v>
+        <v>37668.01</v>
       </c>
     </row>
     <row r="43">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11622.2</v>
+        <v>11564.16</v>
       </c>
     </row>
     <row r="44">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26398.81</v>
+        <v>26266.96</v>
       </c>
     </row>
     <row r="45">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16369.88</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="46">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>30032.48</v>
+        <v>29953.39</v>
       </c>
     </row>
     <row r="47">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>66157.17</v>
+        <v>65982.95</v>
       </c>
     </row>
     <row r="48">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13819.46</v>
+        <v>13783.07</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9428.639999999999</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>25881.76</v>
+        <v>26051.5</v>
       </c>
     </row>
     <row r="51">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10638.79</v>
+        <v>10708.56</v>
       </c>
     </row>
     <row r="52">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20100.15</v>
+        <v>20231.97</v>
       </c>
     </row>
     <row r="53">
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>429970.89</v>
+        <v>431038</v>
       </c>
     </row>
     <row r="54">
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>80553.58</v>
+        <v>80753.5</v>
       </c>
     </row>
     <row r="55">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>16646.57</v>
+        <v>16687.89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LAHUEN HEALTH SERVICES SPA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>G-TALENT SPA</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,11 @@
           <t>77.714.387-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -766,7 +770,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>359-267-SE26</t>
+          <t>1057547-1927-SE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -781,42 +785,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.608.404-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Instituto Nacional del Cancer</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Lahuen Health Services SpA</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.227.643-7</t>
+          <t>77.160.932-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -825,13 +829,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7459.5</v>
+        <v>50881.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>45-527-CM25</t>
+          <t>359-267-SE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -846,22 +850,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.608.404-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>Instituto Nacional del Cancer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -871,28 +875,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.227.643-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>254565.52</v>
+        <v>7459.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233623-15-CM26</t>
+          <t>45-527-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -917,43 +925,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>22718.57</v>
+        <v>254565.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>759-28-CM26</t>
+          <t>1233623-15-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -978,43 +990,47 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18509.23</v>
+        <v>22718.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1532-144-CM26</t>
+          <t>759-28-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1034,17 +1050,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.933.400-0</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO REFERENCIAL DE SALUD DR SALVADOR ALLENDE GOSSENS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1054,28 +1070,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>25450.06</v>
+        <v>18509.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>759-29-CM26</t>
+          <t>1532-144-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1100,12 +1120,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>61.933.400-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>CENTRO REFERENCIAL DE SALUD DR SALVADOR ALLENDE GOSSENS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1115,12 +1135,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1130,13 +1150,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20041.62</v>
+        <v>25450.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4301-75-CM26</t>
+          <t>759-29-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1161,43 +1181,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.733.311-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>19846.2</v>
+        <v>20041.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4127-69-CM26</t>
+          <t>4301-75-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1212,7 +1236,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1222,43 +1246,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10787.97</v>
+        <v>19846.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>761-827-CM25</t>
+          <t>4127-69-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,17 +1306,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1298,12 +1326,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1313,13 +1341,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>46399.86</v>
+        <v>10787.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2366-64-CM26</t>
+          <t>761-827-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1334,7 +1362,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1344,27 +1372,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1374,13 +1402,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34277.51</v>
+        <v>46399.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3756-897-CM25</t>
+          <t>2366-64-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1395,7 +1423,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1405,27 +1433,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1435,13 +1463,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>430686.32</v>
+        <v>34277.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2677-36-CM26</t>
+          <t>3756-897-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1456,7 +1484,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1466,43 +1494,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Rayen Salud SpA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>63261.21</v>
+        <v>430686.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1480134-5-CM26</t>
+          <t>2677-36-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1522,32 +1554,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,13 +1589,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8545.73</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45-12-CM26</t>
+          <t>1480134-5-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,22 +1610,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1603,28 +1635,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>74806.8</v>
+        <v>8545.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>711841-49-SE26</t>
+          <t>45-12-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1649,12 +1685,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1664,32 +1700,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>224012.71</v>
+        <v>74806.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057420-102-CM26</t>
+          <t>711841-49-SE26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1714,43 +1746,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8341.08</v>
+        <v>224012.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>1057420-102-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1770,32 +1806,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1805,13 +1841,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>40809.78</v>
+        <v>8341.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>585-26-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1826,7 +1862,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1836,43 +1872,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NOVIS</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.967.100-k</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32127.7</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1725-79-CM26</t>
+          <t>585-26-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1892,32 +1932,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>NOVIS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.967.100-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1927,13 +1967,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>42321.72</v>
+        <v>32127.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057492-697-CM26</t>
+          <t>1725-79-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1948,7 +1988,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1958,27 +1998,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1988,13 +2028,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7535.11</v>
+        <v>42321.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1725-83-CM26</t>
+          <t>1057492-697-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2019,43 +2059,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>48811.95</v>
+        <v>7535.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>585-29-CM26</t>
+          <t>1725-83-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2070,37 +2114,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NOVIS</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.967.100-k</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2110,13 +2154,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>17432.29</v>
+        <v>48811.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45-43-CM26</t>
+          <t>585-29-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2136,17 +2180,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2156,12 +2200,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>NOVIS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>96.967.100-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2171,13 +2215,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>71839.97</v>
+        <v>17432.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2770-43-CM26</t>
+          <t>45-43-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,17 +2241,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2217,12 +2261,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2232,13 +2276,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>111309.26</v>
+        <v>71839.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>619-53-CM26</t>
+          <t>2770-43-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,22 +2297,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2278,12 +2322,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2293,13 +2337,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>72334.02</v>
+        <v>111309.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2341-88-CM26</t>
+          <t>619-53-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2319,17 +2363,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2339,12 +2383,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2354,13 +2398,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15639.94</v>
+        <v>72334.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2546-46-CM26</t>
+          <t>2341-88-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2375,7 +2419,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2385,17 +2429,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2415,13 +2459,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>50705.23</v>
+        <v>15639.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>609-31-SE26</t>
+          <t>2546-46-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2441,52 +2485,48 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7902.37</v>
+        <v>50705.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>585-34-CM26</t>
+          <t>609-31-SE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2506,17 +2546,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2526,28 +2566,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27702.12</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1704-1105-CM26</t>
+          <t>585-34-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2572,43 +2616,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>45592.37</v>
+        <v>27702.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057503-926-CM26</t>
+          <t>1704-1105-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2623,37 +2671,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD LIGARIUS SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.547-0</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2663,13 +2711,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43455.72</v>
+        <v>45592.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>711-697-CM25</t>
+          <t>1057503-926-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2684,7 +2732,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2694,12 +2742,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2709,12 +2757,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Ingenieria de Software Ltda.</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>85.928.600-3</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2724,13 +2772,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>59522.39</v>
+        <v>43455.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1602-19-CM26</t>
+          <t>711-697-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2755,12 +2803,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2770,12 +2818,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>Ingenieria de Software Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>85.928.600-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2785,13 +2833,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>56533.3</v>
+        <v>59522.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5153-348-CM26</t>
+          <t>1602-19-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,17 +2859,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2831,12 +2879,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2846,13 +2894,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>75841.3</v>
+        <v>56533.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5153-349-CM26</t>
+          <t>5153-348-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2900,20 +2948,24 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>77108.33</v>
+        <v>75841.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1480134-8-CM26</t>
+          <t>5153-349-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2928,7 +2980,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2938,12 +2990,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2953,28 +3005,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19615.96</v>
+        <v>77108.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5155-34-CM26</t>
+          <t>1480134-8-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2994,17 +3050,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3014,28 +3070,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FACTORIT Y COMPANIA LIMITADA</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.142.021-6</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>37668.01</v>
+        <v>19615.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1588-22-CM26</t>
+          <t>5155-34-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3060,12 +3120,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3075,12 +3135,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>FACTORIT Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.142.021-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3090,13 +3150,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11564.16</v>
+        <v>37668.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3894-9-CM26</t>
+          <t>1588-22-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3116,17 +3176,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3136,28 +3196,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26266.96</v>
+        <v>11564.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057501-2182-CM26</t>
+          <t>3894-9-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3182,12 +3246,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3197,12 +3261,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3212,13 +3276,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16288.11</v>
+        <v>26266.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2546-25-CM26</t>
+          <t>1057501-2182-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3233,7 +3297,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3243,43 +3307,47 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>29953.39</v>
+        <v>16288.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4754-3-CM26</t>
+          <t>2546-25-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3299,32 +3367,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3334,13 +3402,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>65982.95</v>
+        <v>29953.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1029940-15-CM26</t>
+          <t>4754-3-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,17 +3428,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.370-0</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3380,12 +3448,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3395,13 +3463,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13783.07</v>
+        <v>65982.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3734-150-CM26</t>
+          <t>1029940-15-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3426,43 +3494,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>62.000.370-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>SUBSECRETARIA DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9403.809999999999</v>
+        <v>13783.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4201-62-CM26</t>
+          <t>3734-150-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3477,53 +3549,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26051.5</v>
+        <v>9403.809999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1422825-499-CM26</t>
+          <t>4201-62-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3548,43 +3624,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10708.56</v>
+        <v>26051.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1056854-20-CM26</t>
+          <t>1422825-499-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3609,43 +3689,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20231.97</v>
+        <v>10708.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2216-95-CM26</t>
+          <t>1056854-20-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3660,22 +3744,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3685,28 +3769,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.802.163-5</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>431038</v>
+        <v>20231.97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>587-61-CM26</t>
+          <t>2216-95-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3726,17 +3814,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3746,12 +3834,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.802.163-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3761,13 +3849,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>80753.5</v>
+        <v>431038</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4079-68-CM26</t>
+          <t>587-61-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3792,27 +3880,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3822,6 +3910,71 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
+        <v>80753.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4079-68-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.151.000-k</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
         <v>16687.89</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -2147,7 +2147,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2704,7 +2708,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
